--- a/data_group/r2_weighted_prec.xlsx
+++ b/data_group/r2_weighted_prec.xlsx
@@ -377,12 +377,6 @@
           <t>CBA</t>
         </is>
       </c>
-      <c r="B2">
-        <v>0.1239456383857611</v>
-      </c>
-      <c r="C2">
-        <v>0.8912120647708912</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -390,24 +384,12 @@
           <t>EBA</t>
         </is>
       </c>
-      <c r="B3">
-        <v>0.4521194415198585</v>
-      </c>
-      <c r="C3">
-        <v>0.9281785158473586</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>SBA</t>
         </is>
-      </c>
-      <c r="B4">
-        <v>0.1557172926450161</v>
-      </c>
-      <c r="C4">
-        <v>0.9137643804924901</v>
       </c>
     </row>
   </sheetData>
